--- a/output/2026-09-15_15_Croazia_Pozesko-slavonska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-15_15_Croazia_Pozesko-slavonska_ATEX_Equipment-Services.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-15_15_Croazia_Pozesko-slavonska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-15_15_Croazia_Pozesko-slavonska_ATEX_Equipment-Services.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copertura nazionale; nessuna sede in Požeško-slavonska. Linea prodotto EX-ATEX confermata (ventilatori antideflagranti 'EB EX-ATEX').</t>
+          <t>Copertura nazionale; nessuna sede in Požeško-slavonska. Linea prodotto EX-ATEX confermata (ventilatori antideflagranti 'EB EX-ATEX'). [DUPLICATO — vedi anche: 2026-09-13_08_Croazia_Koprivnicko-krizevacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-09-15_15_Croazia_Pozesko-slavonska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-15_15_Croazia_Pozesko-slavonska_ATEX_Equipment-Services.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copertura nazionale (sedi/filiali a Osijek, Slavonski Brod, Zagreb, Bjelovar, Vukovar). Nessuna sede fisica in Požeško-slavonska; filiale Slavonski Brod la più vicina. Servizi di ispezione/certificazione Ex, non vendita diretta attrezzature.</t>
+          <t>Copertura nazionale (sedi/filiali a Osijek, Slavonski Brod, Zagreb, Bjelovar, Vukovar). Nessuna sede fisica in Požeško-slavonska; filiale Slavonski Brod la più vicina. Servizi di ispezione/certificazione Ex, non vendita diretta attrezzature. [DUPLICATO — vedi anche: 2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copertura nazionale dichiarata; nessuna sede in Požeško-slavonska. Ispezioni Ex, elettroimpiantistica, automazione e installazione impianti industriali.</t>
+          <t>Copertura nazionale dichiarata; nessuna sede in Požeško-slavonska. Ispezioni Ex, elettroimpiantistica, automazione e installazione impianti industriali. [DUPLICATO — vedi anche: 2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
